--- a/output/graficos_regionales_sexo_edad/plot_intra_nacional_o_ocup_a_2020_nacional.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_nacional_o_ocup_a_2020_nacional.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 09:45</t>
+    <t xml:space="preserve">2026-09-18 09:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -76,13 +76,13 @@
     <t xml:space="preserve">15 a 29 años</t>
   </si>
   <si>
-    <t xml:space="preserve">30 a 44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45 a 59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60 o más</t>
+    <t xml:space="preserve">30 a 44 años</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 a 59 años</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desde 60 años</t>
   </si>
 </sst>
 </file>
